--- a/file_list.xlsx
+++ b/file_list.xlsx
@@ -1,171 +1,156 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27316"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_EC9ACF85D73C7E1C59189DAAD021C3B916903471" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="FileList" sheetId="1" r:id="rId1"/>
+    <sheet name="FileList" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
-  <si>
-    <t>Files</t>
-  </si>
-  <si>
-    <t>10.1002%2Fcne.24985_TABLE1.tsv</t>
-  </si>
-  <si>
-    <t>10.1002%2Fcne.24985_TABLE2.tsv</t>
-  </si>
-  <si>
-    <t>10.1007%2Fs004220000205_Figure3.tsv</t>
-  </si>
-  <si>
-    <t>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</t>
-  </si>
-  <si>
-    <t>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</t>
-  </si>
-  <si>
-    <t>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</t>
-  </si>
-  <si>
-    <t>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</t>
-  </si>
-  <si>
-    <t>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</t>
-  </si>
-  <si>
-    <t>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</t>
-  </si>
-  <si>
-    <t>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</t>
-  </si>
-  <si>
-    <t>10.1038%2Fs41598-018-26062-8_TableS1.tsv</t>
-  </si>
-  <si>
-    <t>10.1038%2Fs41598-018-26062-8_TableS5.tsv</t>
-  </si>
-  <si>
-    <t>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</t>
-  </si>
-  <si>
-    <t>10.1126%2Fscience.aaa9101_TableS1.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000124401_TableI.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000323671_SupplementaryTable1.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000323671_SupplementaryTable2.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000323671.ReadMe.md</t>
-  </si>
-  <si>
-    <t>10.1159%2F000437413_Table1.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000437413_Table2.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000437413_Table3.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000437413_Table4.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000437413_Table5.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000452856_TableS1.tsv</t>
-  </si>
-  <si>
-    <t>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</t>
-  </si>
-  <si>
-    <t>10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</t>
-  </si>
-  <si>
-    <t>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</t>
-  </si>
-  <si>
-    <t>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</t>
-  </si>
-  <si>
-    <t>10.3389%25Ffnana.2013.00035.svg</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnana.2013.00035_Table1-a.tsv</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnana.2013.00035_Table1-b.tsv</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnana.2013.00035.ReadMe.md</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnana.2017.00118_Table1.tsv</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</t>
-  </si>
-  <si>
-    <t>10.3389%2Ffnhum.2013.00424.ReadMe.md</t>
-  </si>
-  <si>
-    <t>10.5061%2Fdryad.2r62k7s.ReadMe.md</t>
-  </si>
-  <si>
-    <t>10.5061%2Fdryad.2r62k7s.tsv</t>
-  </si>
-  <si>
-    <t>10.7554%2FeLife.77875_Supplementaryfile3.tsv</t>
-  </si>
-  <si>
-    <t>10.7554%2FeLife.77875_Table1.tsv</t>
-  </si>
-  <si>
-    <t>README.md</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+  <si>
+    <t xml:space="preserve">Files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24985_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24985_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007%2Fs004220000205_Figure3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Tree.nex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_TableS5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fjmammal%2Fgyz043.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1126%2Fscience.aaa9101_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000124401_TableI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671_SupplementaryTable2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000452856_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS8.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%25Ffnana.2013.00035.svg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Table1-a.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Table1-b.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2017.00118_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnhum.2013.00424.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.77875_Supplementaryfile3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.77875_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README.md</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -202,15 +187,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -492,241 +468,237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A43"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5">
       <c r="A5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8">
       <c r="A8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9">
       <c r="A9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10">
       <c r="A10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11">
       <c r="A11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12">
       <c r="A12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13">
       <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14">
       <c r="A14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15">
       <c r="A15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16">
       <c r="A16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17">
       <c r="A17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19">
       <c r="A19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20">
       <c r="A20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21">
       <c r="A21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22">
       <c r="A22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23">
       <c r="A23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24">
       <c r="A24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26">
       <c r="A26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27">
       <c r="A27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28">
       <c r="A28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29">
       <c r="A29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30">
       <c r="A30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31">
       <c r="A31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32">
       <c r="A32" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33">
       <c r="A33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34">
       <c r="A34" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35">
       <c r="A35" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36">
       <c r="A36" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37">
       <c r="A37" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38">
       <c r="A38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39">
       <c r="A39" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40">
       <c r="A40" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41">
       <c r="A41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42">
       <c r="A42" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43">
       <c r="A43" t="s">
         <v>42</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -969,10 +941,19 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4BF6DFC-B7E6-4C2D-A0AC-1DF81744AD9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18F8EFF1-C37F-4574-B6C9-76657FEC01B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{058565AD-0991-4B54-A22B-80028A03C4B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A12CB3B-C0FE-4606-A982-EBE366E55296}"/>
 </file>
--- a/file_list.xlsx
+++ b/file_list.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">Files</t>
   </si>
@@ -69,6 +69,12 @@
   </si>
   <si>
     <t xml:space="preserve">10.1159%2F000124401_TableI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000319019_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000319019_Table1.tsv</t>
   </si>
   <si>
     <t xml:space="preserve">10.1159%2F000323671_SupplementaryTable1.tsv</t>
@@ -692,6 +698,16 @@
         <v>43</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -951,9 +967,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18F8EFF1-C37F-4574-B6C9-76657FEC01B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C36BB896-5DC0-4207-9EE0-59065ABB3BE1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A12CB3B-C0FE-4606-A982-EBE366E55296}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACE948-7E2F-451F-9CA5-8A0C1B96A0A3}"/>
 </file>